--- a/artfynd/A 8696-2025 artfynd.xlsx
+++ b/artfynd/A 8696-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123485455</v>
       </c>
       <c r="B2" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 8696-2025 artfynd.xlsx
+++ b/artfynd/A 8696-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123485455</v>
       </c>
       <c r="B2" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 8696-2025 artfynd.xlsx
+++ b/artfynd/A 8696-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123485455</v>
       </c>
       <c r="B2" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 8696-2025 artfynd.xlsx
+++ b/artfynd/A 8696-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123485455</v>
       </c>
       <c r="B2" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
